--- a/filer/75206119_dan_cake_a_s.xlsx
+++ b/filer/75206119_dan_cake_a_s.xlsx
@@ -7955,7 +7955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8518,22 +8518,24 @@
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossRelatedToInvestments</t>
+          <t>fsa:RaisingOfLongtermDebt</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossRelatedToInvestments</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n"/>
+          <t>fsa:RaisingOfLongtermDebt</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="n">
+        <v>21828</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>123</v>
+      </c>
       <c r="F18" s="38" t="n">
-        <v>11931</v>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>14073</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
       <c r="I18" s="39" t="inlineStr">
         <is>
@@ -8549,23 +8551,19 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfLongtermDebt</t>
+          <t>fsa:ReceivedDividendsFromAssociates</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfLongtermDebt</t>
+          <t>fsa:ReceivedDividendsFromAssociates</t>
         </is>
       </c>
       <c r="D19" s="35" t="n">
-        <v>21828</v>
-      </c>
-      <c r="E19" s="35" t="n">
-        <v>123</v>
-      </c>
-      <c r="F19" s="35" t="n">
-        <v>0</v>
-      </c>
+        <v>14302</v>
+      </c>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
       <c r="G19" s="35" t="n"/>
       <c r="H19" s="35" t="n"/>
       <c r="I19" s="36" t="inlineStr">
@@ -8582,21 +8580,29 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReceivedDividendsFromAssociates</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReceivedDividendsFromAssociates</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="D20" s="38" t="n">
-        <v>14302</v>
-      </c>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="38" t="n"/>
-      <c r="G20" s="38" t="n"/>
-      <c r="H20" s="38" t="n"/>
+        <v>-25596</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>-34073</v>
+      </c>
+      <c r="F20" s="38" t="n">
+        <v>3297</v>
+      </c>
+      <c r="G20" s="38" t="n">
+        <v>12738</v>
+      </c>
+      <c r="H20" s="38" t="n">
+        <v>20218</v>
+      </c>
       <c r="I20" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8611,29 +8617,21 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:ReversalsOfRevaluationOfDisposedInvestments</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>-25596</v>
-      </c>
-      <c r="E21" s="35" t="n">
-        <v>-34073</v>
-      </c>
+          <t>fsa:ReversalsOfRevaluationOfDisposedInvestments</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
       <c r="F21" s="35" t="n">
-        <v>3297</v>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>12738</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>20218</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
       <c r="I21" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8648,21 +8646,25 @@
       </c>
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReversalsOfRevaluationOfDisposedInvestments</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="C22" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReversalsOfRevaluationOfDisposedInvestments</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="D22" s="38" t="n"/>
       <c r="E22" s="38" t="n"/>
       <c r="F22" s="38" t="n">
+        <v>478</v>
+      </c>
+      <c r="G22" s="38" t="n">
+        <v>561</v>
+      </c>
+      <c r="H22" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="38" t="n"/>
-      <c r="H22" s="38" t="n"/>
       <c r="I22" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8677,24 +8679,26 @@
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n"/>
+      <c r="E23" s="35" t="n">
+        <v>4145</v>
+      </c>
       <c r="F23" s="35" t="n">
-        <v>478</v>
+        <v>4124</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>561</v>
+        <v>3464</v>
       </c>
       <c r="H23" s="35" t="n">
-        <v>0</v>
+        <v>4513</v>
       </c>
       <c r="I23" s="36" t="inlineStr">
         <is>
@@ -8710,65 +8714,30 @@
       </c>
       <c r="B24" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D24" s="38" t="n"/>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
+        </is>
+      </c>
+      <c r="D24" s="38" t="n">
+        <v>-588</v>
+      </c>
       <c r="E24" s="38" t="n">
-        <v>4145</v>
+        <v>-217</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>4124</v>
+        <v>-1376</v>
       </c>
       <c r="G24" s="38" t="n">
-        <v>3464</v>
+        <v>-484</v>
       </c>
       <c r="H24" s="38" t="n">
-        <v>4513</v>
+        <v>-1827</v>
       </c>
       <c r="I24" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="inlineStr">
-        <is>
-          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>-588</v>
-      </c>
-      <c r="E25" s="35" t="n">
-        <v>-217</v>
-      </c>
-      <c r="F25" s="35" t="n">
-        <v>-1376</v>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>-484</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>-1827</v>
-      </c>
-      <c r="I25" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
